--- a/ora_resultado_renal540_diseases.xlsx
+++ b/ora_resultado_renal540_diseases.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2cd7fd51b7c34e8/Desktop/ongoing/Rproj/SofiaAnalise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2254FDC58F79A8D366075C52F37BD2729ACE0E23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61D8FB5F-4296-4E57-AFA3-0C22E68AB7E6}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_2254FDC58F79A8D366075C52F37BD2729ACE0E23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B63C2F-656A-40D9-B6BC-9DE451A442D8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6969" uniqueCount="2237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7028" uniqueCount="2237">
   <si>
     <t>ID</t>
   </si>
@@ -6794,6 +6795,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47490,4 +47495,336 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCFC0881-1557-4B40-8E79-867767C780C0}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="8" max="8" width="68" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>1.6407859241943269E-7</v>
+      </c>
+      <c r="F2">
+        <v>2.283974006478504E-4</v>
+      </c>
+      <c r="G2">
+        <v>1.5768816303046539E-4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>1.631167376995461E-6</v>
+      </c>
+      <c r="F3">
+        <v>3.1390960060177612E-4</v>
+      </c>
+      <c r="G3">
+        <v>2.1672675843120199E-4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4">
+        <v>1.304608820856348E-5</v>
+      </c>
+      <c r="F4">
+        <v>9.3539236682401827E-4</v>
+      </c>
+      <c r="G4">
+        <v>6.4580552851658255E-4</v>
+      </c>
+      <c r="H4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5">
+        <v>1.337194208838163E-5</v>
+      </c>
+      <c r="F5">
+        <v>9.3539236682401827E-4</v>
+      </c>
+      <c r="G5">
+        <v>6.4580552851658255E-4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6">
+        <v>1.343954550034509E-5</v>
+      </c>
+      <c r="F6">
+        <v>9.3539236682401827E-4</v>
+      </c>
+      <c r="G6">
+        <v>6.4580552851658255E-4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7">
+        <v>8.9287066200592087E-5</v>
+      </c>
+      <c r="F7">
+        <v>3.8839873797257558E-3</v>
+      </c>
+      <c r="G7">
+        <v>2.6815490605638348E-3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8">
+        <v>2.194260395902617E-4</v>
+      </c>
+      <c r="F8">
+        <v>7.8819012135443334E-3</v>
+      </c>
+      <c r="G8">
+        <v>5.4417542407486216E-3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9">
+        <v>2.3281492721192041E-4</v>
+      </c>
+      <c r="F9">
+        <v>7.8819012135443334E-3</v>
+      </c>
+      <c r="G9">
+        <v>5.4417542407486216E-3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10">
+        <v>2.9142428832100052E-4</v>
+      </c>
+      <c r="F10">
+        <v>8.8187523770181016E-3</v>
+      </c>
+      <c r="G10">
+        <v>6.088566939063466E-3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11">
+        <v>3.1455069668038458E-4</v>
+      </c>
+      <c r="F11">
+        <v>9.1219702037311536E-3</v>
+      </c>
+      <c r="G11">
+        <v>6.2979119752015617E-3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>